--- a/artfynd/A 3199-2022 artfynd.xlsx
+++ b/artfynd/A 3199-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136018947</v>
       </c>
       <c r="B2" t="n">
-        <v>58136</v>
+        <v>58138</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 3199-2022 artfynd.xlsx
+++ b/artfynd/A 3199-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136018947</v>
       </c>
       <c r="B2" t="n">
-        <v>58138</v>
+        <v>58139</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 3199-2022 artfynd.xlsx
+++ b/artfynd/A 3199-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136018947</v>
       </c>
       <c r="B2" t="n">
-        <v>58139</v>
+        <v>58143</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 3199-2022 artfynd.xlsx
+++ b/artfynd/A 3199-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136018947</v>
       </c>
       <c r="B2" t="n">
-        <v>58143</v>
+        <v>58144</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 3199-2022 artfynd.xlsx
+++ b/artfynd/A 3199-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136018947</v>
       </c>
       <c r="B2" t="n">
-        <v>58144</v>
+        <v>58149</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 3199-2022 artfynd.xlsx
+++ b/artfynd/A 3199-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136018947</v>
       </c>
       <c r="B2" t="n">
-        <v>58149</v>
+        <v>58162</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
